--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA2B\Desktop\hukuoka\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12250" firstSheet="3" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21580" windowHeight="9330" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="大体の流れ" sheetId="1" r:id="rId1"/>
     <sheet name="ステージ" sheetId="3" r:id="rId2"/>
     <sheet name="プレイヤー" sheetId="2" r:id="rId3"/>
-    <sheet name="1ステージ分(α)" sheetId="8" r:id="rId4"/>
+    <sheet name="アイテム" sheetId="9" r:id="rId4"/>
+    <sheet name="1ステージ分(α)" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -306,10 +307,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージオブジェクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -334,7 +331,57 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スライディング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Slide</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>栄養ドリンク</t>
+    <rPh sb="0" eb="2">
+      <t>エイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>栄養ドリンク</t>
+    <rPh sb="0" eb="2">
+      <t>エイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピードアップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２オブジェクト</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -342,7 +389,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,8 +473,16 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,6 +502,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,7 +534,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -487,8 +547,11 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -504,21 +567,25 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="チェック セル" xfId="3" builtinId="23"/>
+    <cellStyle name="どちらでもない" xfId="4" builtinId="28"/>
     <cellStyle name="悪い" xfId="2" builtinId="27"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="1" builtinId="26"/>
@@ -1065,7 +1132,7 @@
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
@@ -1074,7 +1141,7 @@
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="C18" s="8"/>
       <c r="D18" t="s">
         <v>25</v>
       </c>
@@ -1086,7 +1153,7 @@
       <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="5"/>
+      <c r="C19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1101,7 +1168,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="19.4140625" customWidth="1"/>
+    <col min="2" max="2" width="56.4140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="53.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1112,7 +1203,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="38.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
@@ -1120,7 +1211,7 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B2" t="s">
@@ -1128,7 +1219,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B3" t="s">
@@ -1144,47 +1235,47 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>34</v>
+      <c r="A14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1194,27 +1285,35 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>45</v>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -1223,11 +1322,32 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21580" windowHeight="9330" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21585" windowHeight="9330" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="大体の流れ" sheetId="1" r:id="rId1"/>
     <sheet name="ステージ" sheetId="3" r:id="rId2"/>
     <sheet name="プレイヤー" sheetId="2" r:id="rId3"/>
     <sheet name="アイテム" sheetId="9" r:id="rId4"/>
-    <sheet name="1ステージ分(α)" sheetId="8" r:id="rId5"/>
+    <sheet name="β" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -223,42 +223,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1ステージ目</t>
-    <rPh sb="5" eb="6">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>流れ</t>
-    <rPh sb="0" eb="1">
-      <t>ナガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤーのシステム→ステージ→ギミック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>難易度</t>
-    <rPh sb="0" eb="3">
-      <t>ナンイド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>初級（ほぼチュートリアル）</t>
-    <rPh sb="0" eb="2">
-      <t>ショキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>できたら〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -351,10 +315,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アイテム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>栄養ドリンク</t>
     <rPh sb="0" eb="2">
       <t>エイヨウ</t>
@@ -362,26 +322,52 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>栄養ドリンク</t>
+    <t>スピードアップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム(三種類ぐらい)</t>
+    <rPh sb="5" eb="8">
+      <t>サンシュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>足早くなる</t>
     <rPh sb="0" eb="2">
-      <t>エイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スピードアップ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ１オブジェクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ２オブジェクト</t>
+      <t>アシハヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無敵</t>
+    <rPh sb="0" eb="2">
+      <t>ムテキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -389,7 +375,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,14 +418,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,15 +443,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
@@ -482,7 +451,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,16 +470,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -518,36 +482,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -564,28 +510,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="4">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="チェック セル" xfId="3" builtinId="23"/>
-    <cellStyle name="どちらでもない" xfId="4" builtinId="28"/>
+  <cellStyles count="4">
+    <cellStyle name="どちらでもない" xfId="3" builtinId="28"/>
     <cellStyle name="悪い" xfId="2" builtinId="27"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="1" builtinId="26"/>
@@ -983,19 +928,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.58203125" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
     <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="17.08203125" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1031,52 +976,52 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="1" max="1" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1093,14 +1038,14 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="43.08203125" customWidth="1"/>
+    <col min="4" max="4" width="43.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1108,13 +1053,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1125,7 +1070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1134,7 +1079,7 @@
       </c>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1146,7 +1091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1169,21 +1114,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.4140625" customWidth="1"/>
-    <col min="2" max="2" width="56.4140625" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="56.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="53.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="53.45" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1192,162 +1137,162 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="47.58203125" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" customWidth="1"/>
-    <col min="4" max="4" width="28.4140625" customWidth="1"/>
-    <col min="5" max="5" width="30.9140625" customWidth="1"/>
+    <col min="2" max="2" width="47.625" customWidth="1"/>
+    <col min="3" max="3" width="26.125" customWidth="1"/>
+    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="38.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="19" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="7" t="s">
+    <row r="1" spans="1:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="6"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="7" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="4" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="6" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="4" t="s">
+      <c r="B21" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="5" t="s">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -311,10 +311,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>△</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>栄養ドリンク</t>
     <rPh sb="0" eb="2">
       <t>エイヨウ</t>
@@ -326,14 +322,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージ１オブジェクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージ２オブジェクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -367,6 +355,25 @@
     <t>無敵</t>
     <rPh sb="0" eb="2">
       <t>ムテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ１</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計7</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -375,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,16 +449,8 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,11 +467,6 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -483,7 +477,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,9 +485,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -519,18 +510,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3">
-      <alignment vertical="center"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="どちらでもない" xfId="3" builtinId="28"/>
+  <cellStyles count="3">
     <cellStyle name="悪い" xfId="2" builtinId="27"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="良い" xfId="1" builtinId="26"/>
@@ -1122,10 +1112,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="53.45" customHeight="1" x14ac:dyDescent="0.4"/>
@@ -1137,7 +1127,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1147,7 +1137,7 @@
     <col min="5" max="5" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="38.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>33</v>
@@ -1179,24 +1169,26 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>47</v>
+      <c r="B7" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
@@ -1245,7 +1237,9 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="B17" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="3" t="s">
@@ -1254,7 +1248,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>34</v>
@@ -1262,37 +1256,52 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B29" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21585" windowHeight="9330" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21590" windowHeight="9330" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="大体の流れ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -375,6 +375,10 @@
     <rPh sb="0" eb="1">
       <t>ケイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコアアイテム</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -514,10 +518,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -918,19 +922,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="15.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -966,52 +970,52 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="21.125" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1028,14 +1032,14 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="43.125" customWidth="1"/>
+    <col min="4" max="4" width="43.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1043,13 +1047,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1060,35 +1064,35 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="8"/>
+      <c r="C18" s="9"/>
       <c r="D18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="8"/>
+      <c r="C19" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1104,13 +1108,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="56.375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>47</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="53.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:2" ht="53.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1128,17 +1132,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="47.625" customWidth="1"/>
-    <col min="3" max="3" width="26.125" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
-    <col min="5" max="5" width="30.875" customWidth="1"/>
+    <col min="2" max="2" width="47.58203125" customWidth="1"/>
+    <col min="3" max="3" width="26.08203125" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -1146,13 +1150,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -1160,7 +1164,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
@@ -1168,7 +1172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>46</v>
       </c>
@@ -1176,7 +1180,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
         <v>50</v>
       </c>
@@ -1184,18 +1188,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7"/>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1203,7 +1207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
@@ -1211,7 +1215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1219,7 +1223,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
@@ -1227,7 +1231,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
         <v>35</v>
       </c>
@@ -1235,18 +1239,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
-      <c r="B17" s="9">
+      <c r="B17" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
@@ -1254,7 +1258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
@@ -1262,17 +1266,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B22">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4" t="s">
         <v>54</v>
       </c>
@@ -1280,7 +1284,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
         <v>55</v>
       </c>
@@ -1288,19 +1292,21 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" s="4"/>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B29" s="9" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="8" t="s">
         <v>59</v>
       </c>
     </row>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -326,18 +326,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Attack</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイテム(三種類ぐらい)</t>
     <rPh sb="5" eb="8">
       <t>サンシュルイ</t>
@@ -379,6 +367,10 @@
   </si>
   <si>
     <t>スコアアイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1177,22 +1169,12 @@
         <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7"/>
-      <c r="B9" s="8">
-        <v>1</v>
-      </c>
+      <c r="B9" s="8"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
@@ -1252,7 +1234,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>34</v>
@@ -1260,7 +1242,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>28</v>
@@ -1273,31 +1255,31 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>49</v>
+      <c r="A24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>52</v>
+      <c r="A26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -1307,7 +1289,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21590" windowHeight="9330" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21585" windowHeight="9330" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="大体の流れ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -256,10 +256,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>攻撃</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
@@ -322,10 +318,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイテム(三種類ぐらい)</t>
     <rPh sb="5" eb="8">
       <t>サンシュルイ</t>
@@ -355,10 +347,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージ２</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>計7</t>
     <rPh sb="0" eb="1">
       <t>ケイ</t>
@@ -371,6 +359,40 @@
   </si>
   <si>
     <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>セレクト画面</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ２</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>×</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -914,19 +936,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.58203125" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
     <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="17.08203125" customWidth="1"/>
+    <col min="5" max="5" width="17.125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -949,7 +971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -962,52 +984,52 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="1" max="1" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1024,14 +1046,14 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="43.08203125" customWidth="1"/>
+    <col min="4" max="4" width="43.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1039,13 +1061,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1056,7 +1078,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1065,7 +1087,7 @@
       </c>
       <c r="C17" s="9"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1077,7 +1099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1100,21 +1122,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="56.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.375" customWidth="1"/>
+    <col min="2" max="2" width="56.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="53.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    </row>
+    <row r="2" spans="1:2" ht="53.45" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1123,18 +1145,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="47.58203125" customWidth="1"/>
-    <col min="3" max="3" width="26.08203125" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="47.625" customWidth="1"/>
+    <col min="3" max="3" width="26.125" customWidth="1"/>
+    <col min="4" max="4" width="28.375" customWidth="1"/>
+    <col min="5" max="5" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -1142,46 +1164,46 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5" t="s">
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1189,107 +1211,133 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
       <c r="B17" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="4" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27">
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B33">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="8" t="s">
-        <v>56</v>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+      <c r="B35" s="8" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -393,6 +393,42 @@
   </si>
   <si>
     <t>×</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゴールアニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死にアニメーション</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パッケージ化のレベル遷移のバグ</t>
+    <rPh sb="5" eb="6">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの難易度</t>
+    <rPh sb="5" eb="8">
+      <t>ナンイド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1145,10 +1181,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="38.625" customWidth="1"/>
     <col min="2" max="2" width="47.625" customWidth="1"/>
     <col min="3" max="3" width="26.125" customWidth="1"/>
     <col min="4" max="4" width="28.375" customWidth="1"/>
@@ -1330,14 +1366,42 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B33">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B35" s="8" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/アンリアル仕様書 1 1.xlsx
+++ b/アンリアル仕様書 1 1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21585" windowHeight="9330" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21590" windowHeight="9330" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="大体の流れ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>タイトル画面</t>
     <rPh sb="4" eb="6">
@@ -425,6 +425,14 @@
   </si>
   <si>
     <t>BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -972,19 +980,19 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="15.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="17.125" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="17.75" customWidth="1"/>
     <col min="8" max="8" width="16.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1015,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1020,52 +1028,52 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="21.125" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="68.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" ht="47.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:1" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1082,14 +1090,14 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="43.125" customWidth="1"/>
+    <col min="4" max="4" width="43.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1097,13 +1105,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="50.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="15" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1114,7 +1122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1123,7 +1131,7 @@
       </c>
       <c r="C17" s="9"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1135,7 +1143,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1158,13 +1166,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="19.375" customWidth="1"/>
-    <col min="2" max="2" width="56.375" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -1172,7 +1180,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="53.45" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:2" ht="53.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1182,17 +1190,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B40"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="38.625" customWidth="1"/>
-    <col min="2" max="2" width="47.625" customWidth="1"/>
-    <col min="3" max="3" width="26.125" customWidth="1"/>
-    <col min="4" max="4" width="28.375" customWidth="1"/>
-    <col min="5" max="5" width="30.875" customWidth="1"/>
+    <col min="1" max="1" width="38.58203125" customWidth="1"/>
+    <col min="2" max="2" width="47.58203125" customWidth="1"/>
+    <col min="3" max="3" width="26.08203125" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -1200,13 +1208,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
@@ -1214,7 +1222,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
@@ -1222,7 +1230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
         <v>45</v>
       </c>
@@ -1230,16 +1238,16 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
@@ -1247,7 +1255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
         <v>31</v>
       </c>
@@ -1255,7 +1263,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1263,7 +1271,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
@@ -1271,7 +1279,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
         <v>34</v>
       </c>
@@ -1279,18 +1287,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
       <c r="B17" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
         <v>57</v>
       </c>
@@ -1298,12 +1306,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5" t="s">
         <v>59</v>
       </c>
@@ -1311,12 +1319,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
         <v>52</v>
       </c>
@@ -1324,7 +1332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4" t="s">
         <v>61</v>
       </c>
@@ -1332,17 +1340,17 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5" t="s">
         <v>49</v>
       </c>
@@ -1350,7 +1358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4" t="s">
         <v>50</v>
       </c>
@@ -1358,7 +1366,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5" t="s">
         <v>54</v>
       </c>
@@ -1366,27 +1374,33 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -1394,12 +1408,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>66</v>
       </c>
